--- a/output/2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,6 @@
           <t>Centum</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -536,7 +535,6 @@
           <t>011/2084-315</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Rappresentante e distributore esclusivo di utensili e attrezzature industriali. Verificato su planplus.rs.</t>
@@ -554,7 +552,6 @@
           <t>Fin Import</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -570,7 +567,6 @@
           <t>011/3657-204</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Distributore di attrezzature per saldatura e taglio metalli. Verificato su planplus.rs.</t>
@@ -578,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -588,7 +584,6 @@
           <t>Kordun-Elektro</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -604,7 +599,6 @@
           <t>011/239-2306</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Macchine e utensili (nome suggerisce anche commercio elettrico). Verificato su planplus.rs, confidenza media.</t>
@@ -622,7 +616,6 @@
           <t>Teximp d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -638,7 +631,6 @@
           <t>011/7129-428</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Distributore macchine CNC, torni, centri di lavorazione, utensili (rappresenta Haas, Nakamura-Tome, Tornos, Matsuura). Azienda internazionale, presente in 8 paesi Sud-Est Europa.</t>
@@ -646,7 +638,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -676,7 +668,6 @@
           <t>+381 11 314 90 38</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Rappresentante ufficiale ISCAR per Serbia e Montenegro (sede Zemun, filiale Užice). Verificato su sito ufficiale.</t>
@@ -694,7 +685,6 @@
           <t>UTS Balkan Tools</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -705,8 +695,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Joint-venture italo-serba specializzata in utensili da taglio/manuali (confermata da articolo RNIDS 2018). Dominio non raggiungibile al momento della verifica.</t>
@@ -714,7 +702,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -724,7 +712,6 @@
           <t>Lenex</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -735,8 +722,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Macchine utensili/attrezzature industriali. Verificato su machinetools.com e planplus.rs.</t>
@@ -754,7 +739,6 @@
           <t>D&amp;S Profi Alati (D&amp;S Alati)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -770,7 +754,6 @@
           <t>011/664-6334</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Negozio di utensili professionali. Verificato su planplus.rs.</t>
@@ -778,7 +761,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -788,7 +771,6 @@
           <t>DABS Alati</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -804,7 +786,6 @@
           <t>011/313-3351</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Vendita di utensili professionali. Verificato su planplus.rs.</t>
@@ -812,7 +793,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -822,7 +803,6 @@
           <t>Entuziast</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -838,7 +818,6 @@
           <t>011/252-0098</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Utensili e macchine professionali. Verificato su planplus.rs.</t>
@@ -856,7 +835,6 @@
           <t>Fero Tools</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -872,7 +850,6 @@
           <t>011/613-5832</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Importatore ufficiale brand IAT (utensili). Verificato su planplus.rs.</t>
@@ -880,7 +857,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -890,7 +867,6 @@
           <t>Feromerkur Export</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -906,7 +882,6 @@
           <t>011/318-7330</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Distributore di utensili. Verificato su planplus.rs.</t>
@@ -924,7 +899,6 @@
           <t>Ergo Line</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -940,7 +914,6 @@
           <t>011/265-9662</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Negozio di utensili, compare anche in categoria giardinaggio (focus misto). Verificato su planplus.rs.</t>
@@ -958,7 +931,6 @@
           <t>Force Peđa</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -974,7 +946,6 @@
           <t>062/266-658</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Negozio di utensili, micro-attività con solo cellulare personale. Verificato su planplus.rs, confidenza media.</t>
@@ -992,7 +963,6 @@
           <t>Fortuna (alati i oprema)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1008,7 +978,6 @@
           <t>011/3770-400</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Utensili e attrezzature. Verificato su planplus.rs.</t>
@@ -1016,7 +985,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +995,6 @@
           <t>Gleter-Max</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1042,7 +1010,6 @@
           <t>011/2109-319</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Utensili. Verificato su planplus.rs.</t>
@@ -1060,7 +1027,6 @@
           <t>Iskra Servis</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1076,7 +1042,6 @@
           <t>011/3290-295</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Distributore e assistenza Makita (svolge anche distribuzione, non solo service). Verificato su planplus.rs.</t>
@@ -1084,7 +1049,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1059,6 @@
           <t>ITH Trading</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1110,7 +1074,6 @@
           <t>011/324-0627</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1118,7 +1081,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1091,6 @@
           <t>Interlignum-NS</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1144,7 +1106,6 @@
           <t>011/247-1768</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1162,7 +1123,6 @@
           <t>Hilti Store Belgrade</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1178,7 +1138,6 @@
           <t>011/6556-892</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Utensili professionali, store ufficiale brand Hilti. Esistenza confermata in directory (confidenza media).</t>
@@ -1186,7 +1145,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1155,6 @@
           <t>M.P.A. Mašine Pribor Alati</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1212,7 +1170,6 @@
           <t>011/3563-635</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Macchine, accessori e utensili. Verificato su planplus.rs. Possibile affiliazione con M.P.A. Petrović (stesso gruppo familiare), profili distinti.</t>
@@ -1230,7 +1187,6 @@
           <t>M.P.A. Petrović</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1241,8 +1197,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs come profilo distinto da M.P.A. Mašine Pribor Alati.</t>
@@ -1260,7 +1214,6 @@
           <t>Manojlović GZ</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1276,7 +1229,6 @@
           <t>011/311-5474</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Utensili professionali. Verificato su planplus.rs.</t>
@@ -1294,7 +1246,6 @@
           <t>Simet - mašine i alati</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1310,7 +1261,6 @@
           <t>011/311-5613</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1318,7 +1268,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1278,6 @@
           <t>SIT Systems - mašine i alati</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1344,7 +1293,6 @@
           <t>011/409-2614</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1362,7 +1310,6 @@
           <t>Sterus - alati i HTZ oprema</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1378,7 +1325,6 @@
           <t>011/3572-590</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Utensili e dispositivi di protezione individuale (HTZ). Verificato su planplus.rs.</t>
@@ -1386,7 +1332,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1342,6 @@
           <t>Stridon Group</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1412,7 +1357,6 @@
           <t>011/2100-230</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Distributore elettroutensili Bosch, multi-sede a Belgrado. Verificato su planplus.rs.</t>
@@ -1420,7 +1364,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1374,6 @@
           <t>Tim Komerc</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1446,7 +1389,6 @@
           <t>011/3984-584</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Vendita di utensili e attrezzature. Verificato su planplus.rs.</t>
@@ -1464,7 +1406,6 @@
           <t>Unior Teos Alati</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1480,7 +1421,6 @@
           <t>011/2412-555</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Utensili manuali (brand Unior). Conferma debole, senza pagina di dettaglio diretta: confidenza media.</t>
@@ -1498,7 +1438,6 @@
           <t>Wagner - mašine i alati</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1514,7 +1453,6 @@
           <t>011/232-2741</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1532,7 +1470,6 @@
           <t>Wemaro Alati</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1548,7 +1485,6 @@
           <t>065/277-8187</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Utensili. Verificato su planplus.rs.</t>
@@ -1566,7 +1502,6 @@
           <t>Woby Haus</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1582,7 +1517,6 @@
           <t>011/218-4490</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Macchine e utensili, vendita multi-sede (Zvezdara, Čukarica, Zemun). Verificato su planplus.rs.</t>
@@ -1600,7 +1534,6 @@
           <t>Pick &amp; Go (rivenditore Würth)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1616,7 +1549,6 @@
           <t>062/684-920</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Punto vendita ufficiale Würth Pick&amp;Go a Palilula. Confermato.</t>
@@ -1624,7 +1556,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1566,6 @@
           <t>Selectra</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1645,8 +1576,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Distribuzione prodotti Tyrolit (abrasivi/utensili). Verificato su planplus.rs.</t>
@@ -1654,7 +1583,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1593,6 @@
           <t>Bito Group</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1680,7 +1608,6 @@
           <t>011/412-6018</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Distributore autorizzato PROXXON Micromot (utensili di precisione). Verificato su planplus.rs.</t>
@@ -1688,7 +1615,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1625,6 @@
           <t>Belanović</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1714,7 +1640,6 @@
           <t>011/7544-387</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Elettroutensili professionali Makita. Verificato su planplus.rs.</t>
@@ -1722,7 +1647,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1657,6 @@
           <t>BTS Company</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1748,7 +1672,6 @@
           <t>011/2656-068</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1766,7 +1689,6 @@
           <t>Ecomex</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1782,7 +1704,6 @@
           <t>011/3016-309</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
@@ -1800,7 +1721,6 @@
           <t>Elumatec</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1816,7 +1736,6 @@
           <t>011/2394-832</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Macchine per lavorazione alluminio/PVC/acciaio (possibile rivenditore). Nessuna conferma diretta di affiliazione col produttore tedesco Elumatec AG: confidenza media.</t>
@@ -1824,7 +1743,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1753,6 @@
           <t>Gates</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1850,7 +1768,6 @@
           <t>011/307-7426</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Macchine e utensili (generico). Nessuna conferma di legame col brand Gates Corporation, probabile omonimia.</t>
@@ -1868,7 +1785,6 @@
           <t>Beotehnology</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -1884,7 +1800,6 @@
           <t>011/2589-569</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Macchine e utensili. Verificato su planplus.rs.</t>
